--- a/VerveStacks_MEX/vt_vervestacks_MEX_v1.xlsx
+++ b/VerveStacks_MEX/vt_vervestacks_MEX_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2D5A374-53B8-494B-9FBF-2E52D4FE5DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEC0FC5F-F0C8-4670-865F-4B4AD51F01BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2CA455F6-11ED-4E72-86E4-C0DF73E7B8DE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8C160CBC-D6C8-4FC8-BA8A-A803257192F7}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3289,7 +3289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7561E0C-2AC4-4922-AA03-6A85E76DAF3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CEC1BB9-114A-4C82-A3F4-3D925E40D687}">
   <dimension ref="B9:T142"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3368,7 +3368,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.10069392000000002</v>
+        <v>7.350656160000002E-2</v>
       </c>
       <c r="F11">
         <v>3583</v>
@@ -3424,19 +3424,19 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.13364999999999999</v>
+        <v>7.323360000000001E-2</v>
       </c>
       <c r="F12">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G12">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H12">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I12">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -3480,19 +3480,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.13364999999999999</v>
+        <v>7.323360000000001E-2</v>
       </c>
       <c r="F13">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G13">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H13">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I13">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J13" t="s">
         <v>20</v>
@@ -3536,19 +3536,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.13364999999999999</v>
+        <v>7.323360000000001E-2</v>
       </c>
       <c r="F14">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G14">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H14">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I14">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J14" t="s">
         <v>21</v>
@@ -3592,19 +3592,19 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.13364999999999999</v>
+        <v>7.323360000000001E-2</v>
       </c>
       <c r="F15">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G15">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H15">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I15">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -3648,19 +3648,19 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.17784</v>
+        <v>7.9891200000000009E-2</v>
       </c>
       <c r="F16">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G16">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H16">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I16">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J16" t="s">
         <v>23</v>
@@ -3704,19 +3704,19 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.17784</v>
+        <v>7.9891200000000009E-2</v>
       </c>
       <c r="F17">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G17">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H17">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I17">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J17" t="s">
         <v>24</v>
@@ -3760,19 +3760,19 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.17784</v>
+        <v>7.9891200000000009E-2</v>
       </c>
       <c r="F18">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G18">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H18">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I18">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J18" t="s">
         <v>25</v>
@@ -3816,19 +3816,19 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.17784</v>
+        <v>7.9891200000000009E-2</v>
       </c>
       <c r="F19">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G19">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H19">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I19">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J19" t="s">
         <v>26</v>
@@ -3872,19 +3872,19 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.17784</v>
+        <v>7.9891200000000009E-2</v>
       </c>
       <c r="F20">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G20">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H20">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I20">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J20" t="s">
         <v>27</v>
@@ -3928,19 +3928,19 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.17784</v>
+        <v>7.9891200000000009E-2</v>
       </c>
       <c r="F21">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G21">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H21">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I21">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J21" t="s">
         <v>28</v>
@@ -3984,19 +3984,19 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.17784</v>
+        <v>7.9891200000000009E-2</v>
       </c>
       <c r="F22">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G22">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H22">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I22">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J22" t="s">
         <v>29</v>
@@ -4040,19 +4040,19 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.17784</v>
+        <v>7.9891200000000009E-2</v>
       </c>
       <c r="F23">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G23">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H23">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I23">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J23" t="s">
         <v>30</v>
@@ -4096,19 +4096,19 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.17784</v>
+        <v>7.9891200000000009E-2</v>
       </c>
       <c r="F24">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G24">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H24">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I24">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J24" t="s">
         <v>31</v>
@@ -4152,19 +4152,19 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.17784</v>
+        <v>7.9891200000000009E-2</v>
       </c>
       <c r="F25">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G25">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H25">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I25">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J25" t="s">
         <v>32</v>
@@ -4208,19 +4208,19 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.30138500000000001</v>
+        <v>0.20011490000000001</v>
       </c>
       <c r="F26">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="G26">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="H26">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="I26">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J26" t="s">
         <v>33</v>
@@ -4264,7 +4264,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -4320,7 +4320,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -4376,7 +4376,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -4432,7 +4432,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.4393199062709216</v>
+        <v>0.370475</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -4488,7 +4488,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -4544,7 +4544,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -4600,7 +4600,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -4656,7 +4656,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -4712,7 +4712,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -4768,7 +4768,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -4824,7 +4824,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -4880,7 +4880,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -4936,7 +4936,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -4992,7 +4992,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -5048,7 +5048,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.42417094398571747</v>
+        <v>0.35770000000000002</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -5104,7 +5104,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.42417094398571747</v>
+        <v>0.35770000000000002</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -5160,7 +5160,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -5216,7 +5216,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -5272,7 +5272,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -5328,7 +5328,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -5384,7 +5384,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.39766025998661014</v>
+        <v>0.33534375</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -5440,7 +5440,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.34085165141709439</v>
+        <v>0.28743750000000001</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -5496,7 +5496,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -5552,7 +5552,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.39387301941530906</v>
+        <v>0.33214999999999995</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -5608,7 +5608,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -5664,7 +5664,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -5720,7 +5720,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -5776,7 +5776,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -5832,7 +5832,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.41280922227181427</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -5888,7 +5888,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -5944,7 +5944,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -6000,7 +6000,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -6056,7 +6056,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.42417094398571747</v>
+        <v>0.35770000000000002</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -6112,7 +6112,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -6168,7 +6168,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.39387301941530906</v>
+        <v>0.33214999999999995</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -6224,7 +6224,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -6280,7 +6280,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -6336,7 +6336,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -6392,7 +6392,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -6448,7 +6448,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.41280922227181427</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -6504,7 +6504,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.41280922227181427</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -6560,7 +6560,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -6616,7 +6616,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -6672,7 +6672,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.39387301941530906</v>
+        <v>0.33214999999999995</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -6728,7 +6728,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.39766025998661014</v>
+        <v>0.33534375</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -6784,7 +6784,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -6840,7 +6840,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.42417094398571742</v>
+        <v>0.35770000000000002</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -6896,7 +6896,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.39766025998661014</v>
+        <v>0.33534375</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -6952,7 +6952,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -7008,7 +7008,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -7064,7 +7064,7 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -7120,7 +7120,7 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -7176,7 +7176,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -7232,7 +7232,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -7288,7 +7288,7 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.39387301941530906</v>
+        <v>0.33214999999999995</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -7344,7 +7344,7 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.39387301941530906</v>
+        <v>0.33214999999999995</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -7400,7 +7400,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.45446886855612584</v>
+        <v>0.38324999999999998</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -7456,7 +7456,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -7512,7 +7512,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -7568,7 +7568,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -7624,7 +7624,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -7680,7 +7680,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -7736,7 +7736,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -7792,7 +7792,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.42417094398571742</v>
+        <v>0.35770000000000002</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -7848,7 +7848,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.39387301941530906</v>
+        <v>0.33214999999999995</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -7904,7 +7904,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.39387301941530906</v>
+        <v>0.33214999999999995</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -7960,7 +7960,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -8016,7 +8016,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -8072,7 +8072,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -8128,7 +8128,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -8184,7 +8184,7 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.41280922227181432</v>
+        <v>0.34811875000000003</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -8240,7 +8240,7 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -8296,7 +8296,7 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.42417094398571742</v>
+        <v>0.35770000000000002</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -8352,7 +8352,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.42417094398571747</v>
+        <v>0.35770000000000002</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -8408,7 +8408,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.39387301941530906</v>
+        <v>0.33214999999999995</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -8464,7 +8464,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.39387301941530906</v>
+        <v>0.33214999999999995</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -8520,7 +8520,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.39387301941530906</v>
+        <v>0.33214999999999995</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -8576,7 +8576,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -8632,7 +8632,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.45446886855612584</v>
+        <v>0.38325000000000004</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -8688,7 +8688,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.4393199062709216</v>
+        <v>0.370475</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -8744,7 +8744,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.4393199062709216</v>
+        <v>0.37047499999999994</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -8800,7 +8800,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.23480891542066501</v>
+        <v>0.19801250000000001</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -8856,7 +8856,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.23480891542066501</v>
+        <v>0.19801250000000001</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -8912,7 +8912,7 @@
         <v>14</v>
       </c>
       <c r="E110">
-        <v>0.24238339656326713</v>
+        <v>0.20440000000000003</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -8968,7 +8968,7 @@
         <v>14</v>
       </c>
       <c r="E111">
-        <v>0.27268132113367549</v>
+        <v>0.22994999999999999</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -9024,7 +9024,7 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>0.27268132113367549</v>
+        <v>0.22994999999999999</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -9080,7 +9080,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.27268132113367549</v>
+        <v>0.22994999999999999</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -9136,7 +9136,7 @@
         <v>14</v>
       </c>
       <c r="E114">
-        <v>0.24238339656326713</v>
+        <v>0.20440000000000003</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -9192,7 +9192,7 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>0.23480891542066501</v>
+        <v>0.19801250000000001</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -9248,7 +9248,7 @@
         <v>14</v>
       </c>
       <c r="E116">
-        <v>0.25753235884847131</v>
+        <v>0.21717500000000001</v>
       </c>
       <c r="F116">
         <v>1365</v>
@@ -9304,7 +9304,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.25753235884847131</v>
+        <v>0.21717500000000001</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -9360,7 +9360,7 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>0.24238339656326713</v>
+        <v>0.20440000000000003</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -9416,7 +9416,7 @@
         <v>14</v>
       </c>
       <c r="E119">
-        <v>0.23480891542066501</v>
+        <v>0.19801250000000001</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -9472,7 +9472,7 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0.24238339656326713</v>
+        <v>0.20440000000000003</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -9528,7 +9528,7 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>0.24238339656326713</v>
+        <v>0.20440000000000003</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -9584,7 +9584,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <v>0.23480891542066501</v>
+        <v>0.19801250000000001</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -9640,7 +9640,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.23480891542066501</v>
+        <v>0.19801250000000001</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -9696,7 +9696,7 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>0.25753235884847125</v>
+        <v>0.21717499999999998</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -9976,7 +9976,7 @@
         <v>14</v>
       </c>
       <c r="E129">
-        <v>0.37872405713010487</v>
+        <v>0.31937500000000002</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -10032,7 +10032,7 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>0.18178754742245032</v>
+        <v>0.15329999999999999</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -10088,7 +10088,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.24238339656326713</v>
+        <v>0.20440000000000003</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -10144,7 +10144,7 @@
         <v>14</v>
       </c>
       <c r="E132">
-        <v>0.24995787770586919</v>
+        <v>0.21078749999999999</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -10200,7 +10200,7 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>0.24995787770586919</v>
+        <v>0.21078749999999999</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -10256,7 +10256,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.25753235884847131</v>
+        <v>0.21717500000000001</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -10312,7 +10312,7 @@
         <v>14</v>
       </c>
       <c r="E135">
-        <v>0.25753235884847131</v>
+        <v>0.21717500000000001</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -10368,7 +10368,7 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>0.25753235884847131</v>
+        <v>0.21717500000000001</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -10424,7 +10424,7 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>0.25753235884847131</v>
+        <v>0.21717500000000001</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -10480,7 +10480,7 @@
         <v>14</v>
       </c>
       <c r="E138">
-        <v>0.25753235884847131</v>
+        <v>0.21717500000000001</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -10536,7 +10536,7 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>0.25753235884847131</v>
+        <v>0.21717500000000001</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -10592,7 +10592,7 @@
         <v>14</v>
       </c>
       <c r="E140">
-        <v>0.24238339656326713</v>
+        <v>0.20439999999999997</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -10689,7 +10689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33EF57F3-0EA7-4E6F-97C2-C052777F3A1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA2CE59-3D94-426B-B60E-2FA947F01B0C}">
   <dimension ref="B9:T85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14936,7 +14936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E819E48-A10B-4BDD-A73E-CFAAD1153CC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45AFF1E8-60CE-4AAB-A9D7-CFC2D154AEF8}">
   <dimension ref="B9:T401"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15021,7 +15021,7 @@
         <v>0.08</v>
       </c>
       <c r="G11">
-        <v>0.3</v>
+        <v>0.219</v>
       </c>
       <c r="H11">
         <v>4725</v>
@@ -15074,7 +15074,7 @@
         <v>0.14299999999999999</v>
       </c>
       <c r="G12">
-        <v>0.3</v>
+        <v>0.219</v>
       </c>
       <c r="H12">
         <v>4725</v>
@@ -15127,7 +15127,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G13">
-        <v>0.3</v>
+        <v>0.219</v>
       </c>
       <c r="H13">
         <v>4725</v>
@@ -15180,7 +15180,7 @@
         <v>0.05</v>
       </c>
       <c r="G14">
-        <v>0.3</v>
+        <v>0.21899999999999997</v>
       </c>
       <c r="H14">
         <v>4725</v>
@@ -15233,7 +15233,7 @@
         <v>0.56399999999999995</v>
       </c>
       <c r="G15">
-        <v>0.35</v>
+        <v>0.2555</v>
       </c>
       <c r="H15">
         <v>3500</v>
@@ -15286,7 +15286,7 @@
         <v>1.9999999999997797E-3</v>
       </c>
       <c r="G16">
-        <v>0.33123000000000002</v>
+        <v>0.24179790000000001</v>
       </c>
       <c r="K16">
         <v>33</v>
@@ -15330,7 +15330,7 @@
         <v>0.3</v>
       </c>
       <c r="G17">
-        <v>0.33</v>
+        <v>0.24089999999999998</v>
       </c>
       <c r="H17">
         <v>2300</v>
@@ -15383,7 +15383,7 @@
         <v>0.3</v>
       </c>
       <c r="G18">
-        <v>0.33</v>
+        <v>0.24089999999999998</v>
       </c>
       <c r="H18">
         <v>2300</v>
@@ -15436,7 +15436,7 @@
         <v>0.3</v>
       </c>
       <c r="G19">
-        <v>0.33</v>
+        <v>0.24089999999999998</v>
       </c>
       <c r="H19">
         <v>2300</v>
@@ -15489,7 +15489,7 @@
         <v>0.3</v>
       </c>
       <c r="G20">
-        <v>0.33</v>
+        <v>0.24089999999999998</v>
       </c>
       <c r="H20">
         <v>2300</v>
@@ -15542,7 +15542,7 @@
         <v>0.35</v>
       </c>
       <c r="G21">
-        <v>0.36</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H21">
         <v>2000</v>
@@ -15595,7 +15595,7 @@
         <v>0.35</v>
       </c>
       <c r="G22">
-        <v>0.36</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H22">
         <v>2000</v>
@@ -15648,7 +15648,7 @@
         <v>0.35</v>
       </c>
       <c r="G23">
-        <v>0.36</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H23">
         <v>2000</v>
@@ -15701,7 +15701,7 @@
         <v>0.35</v>
       </c>
       <c r="G24">
-        <v>0.36</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H24">
         <v>2000</v>
@@ -15754,7 +15754,7 @@
         <v>0.35</v>
       </c>
       <c r="G25">
-        <v>0.36</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H25">
         <v>2000</v>
@@ -15807,7 +15807,7 @@
         <v>0.35</v>
       </c>
       <c r="G26">
-        <v>0.36</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H26">
         <v>2000</v>
@@ -15860,7 +15860,7 @@
         <v>0.35</v>
       </c>
       <c r="G27">
-        <v>0.36</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H27">
         <v>2000</v>
@@ -15913,7 +15913,7 @@
         <v>0.35</v>
       </c>
       <c r="G28">
-        <v>0.36</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H28">
         <v>2000</v>
@@ -15966,7 +15966,7 @@
         <v>0.35</v>
       </c>
       <c r="G29">
-        <v>0.36</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H29">
         <v>2000</v>
@@ -16019,7 +16019,7 @@
         <v>0.35</v>
       </c>
       <c r="G30">
-        <v>0.36</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H30">
         <v>2000</v>
@@ -16040,7 +16040,7 @@
         <v>34</v>
       </c>
       <c r="P30" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="Q30" t="s">
         <v>352</v>
@@ -16072,7 +16072,7 @@
         <v>0.67800000000000005</v>
       </c>
       <c r="G31">
-        <v>0.39500000000000002</v>
+        <v>0.28835</v>
       </c>
       <c r="H31">
         <v>2200</v>
@@ -16093,7 +16093,7 @@
         <v>34</v>
       </c>
       <c r="P31" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="Q31" t="s">
         <v>352</v>
@@ -16125,7 +16125,7 @@
         <v>0.23980000000000001</v>
       </c>
       <c r="G32">
-        <v>0.32894889533586252</v>
+        <v>0.27739999999999998</v>
       </c>
       <c r="H32">
         <v>1150</v>
@@ -16178,7 +16178,7 @@
         <v>0.33550000000000002</v>
       </c>
       <c r="G33">
-        <v>0.43282749386297698</v>
+        <v>0.36500000000000005</v>
       </c>
       <c r="H33">
         <v>1150</v>
@@ -16231,7 +16231,7 @@
         <v>0.22</v>
       </c>
       <c r="G34">
-        <v>0.43282749386297698</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="H34">
         <v>1150</v>
@@ -16284,7 +16284,7 @@
         <v>0.45200000000000001</v>
       </c>
       <c r="G35">
-        <v>0.43282749386297698</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="H35">
         <v>1150</v>
@@ -16337,7 +16337,7 @@
         <v>0.66600000000000004</v>
       </c>
       <c r="G36">
-        <v>0.43282749386297703</v>
+        <v>0.36499999999999994</v>
       </c>
       <c r="H36">
         <v>1150</v>
@@ -16390,7 +16390,7 @@
         <v>0.22700000000000001</v>
       </c>
       <c r="G37">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H37">
         <v>1150</v>
@@ -16443,7 +16443,7 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="G38">
-        <v>0.45014059361749609</v>
+        <v>0.37960000000000005</v>
       </c>
       <c r="H38">
         <v>1150</v>
@@ -16496,7 +16496,7 @@
         <v>0.32300000000000001</v>
       </c>
       <c r="G39">
-        <v>0.48476679312653431</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H39">
         <v>1150</v>
@@ -16549,7 +16549,7 @@
         <v>0.45960000000000001</v>
       </c>
       <c r="G40">
-        <v>0.4847667931265342</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H40">
         <v>1150</v>
@@ -16602,7 +16602,7 @@
         <v>0.19700000000000001</v>
       </c>
       <c r="G41">
-        <v>0.48476679312653426</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H41">
         <v>1150</v>
@@ -16655,7 +16655,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G42">
-        <v>0.4847667931265342</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H42">
         <v>1150</v>
@@ -16708,7 +16708,7 @@
         <v>0.15</v>
       </c>
       <c r="G43">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H43">
         <v>1150</v>
@@ -16761,7 +16761,7 @@
         <v>0.51400000000000001</v>
       </c>
       <c r="G44">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H44">
         <v>1000</v>
@@ -16814,7 +16814,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="G45">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999989</v>
       </c>
       <c r="H45">
         <v>1000</v>
@@ -16867,7 +16867,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="G46">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999989</v>
       </c>
       <c r="H46">
         <v>1000</v>
@@ -16920,7 +16920,7 @@
         <v>0.45850000000000002</v>
       </c>
       <c r="G47">
-        <v>0.50207989288105326</v>
+        <v>0.4234</v>
       </c>
       <c r="H47">
         <v>1000</v>
@@ -16973,7 +16973,7 @@
         <v>0.874</v>
       </c>
       <c r="G48">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H48">
         <v>1000</v>
@@ -17026,7 +17026,7 @@
         <v>0.86599999999999999</v>
       </c>
       <c r="G49">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H49">
         <v>1000</v>
@@ -17079,7 +17079,7 @@
         <v>0.878</v>
       </c>
       <c r="G50">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H50">
         <v>1000</v>
@@ -17132,7 +17132,7 @@
         <v>0.85</v>
       </c>
       <c r="G51">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H51">
         <v>1000</v>
@@ -17185,7 +17185,7 @@
         <v>0.76600000000000001</v>
       </c>
       <c r="G52">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H52">
         <v>1000</v>
@@ -17238,7 +17238,7 @@
         <v>0.39300000000000002</v>
       </c>
       <c r="G53">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999989</v>
       </c>
       <c r="H53">
         <v>1000</v>
@@ -17291,7 +17291,7 @@
         <v>0.35</v>
       </c>
       <c r="G54">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999989</v>
       </c>
       <c r="H54">
         <v>1000</v>
@@ -17344,7 +17344,7 @@
         <v>0.433</v>
       </c>
       <c r="G55">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H55">
         <v>1000</v>
@@ -17397,7 +17397,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G56">
-        <v>0.47178196831064501</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H56">
         <v>1000</v>
@@ -17450,7 +17450,7 @@
         <v>0.36399999999999999</v>
       </c>
       <c r="G57">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H57">
         <v>1000</v>
@@ -17503,7 +17503,7 @@
         <v>0.2581</v>
       </c>
       <c r="G58">
-        <v>0.48476679312653426</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H58">
         <v>1150</v>
@@ -17556,7 +17556,7 @@
         <v>0.2581</v>
       </c>
       <c r="G59">
-        <v>0.48476679312653426</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H59">
         <v>1150</v>
@@ -17609,7 +17609,7 @@
         <v>0.72699999999999998</v>
       </c>
       <c r="G60">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H60">
         <v>1000</v>
@@ -17662,7 +17662,7 @@
         <v>0.72699999999999998</v>
       </c>
       <c r="G61">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H61">
         <v>1000</v>
@@ -17715,7 +17715,7 @@
         <v>1.0680000000000001</v>
       </c>
       <c r="G62">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H62">
         <v>1000</v>
@@ -17768,7 +17768,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="G63">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H63">
         <v>1000</v>
@@ -17821,7 +17821,7 @@
         <v>0.45900000000000002</v>
       </c>
       <c r="G64">
-        <v>0.45446886855612584</v>
+        <v>0.38324999999999998</v>
       </c>
       <c r="H64">
         <v>1000</v>
@@ -17874,7 +17874,7 @@
         <v>0.378</v>
       </c>
       <c r="G65">
-        <v>0.38954474447667931</v>
+        <v>0.32850000000000001</v>
       </c>
       <c r="H65">
         <v>1000</v>
@@ -17927,7 +17927,7 @@
         <v>0.76879999999999993</v>
       </c>
       <c r="G66">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H66">
         <v>1000.0000000000001</v>
@@ -17980,7 +17980,7 @@
         <v>0.25</v>
       </c>
       <c r="G67">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H67">
         <v>1150</v>
@@ -18033,7 +18033,7 @@
         <v>0.79100000000000004</v>
       </c>
       <c r="G68">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H68">
         <v>1000</v>
@@ -18086,7 +18086,7 @@
         <v>0.77</v>
       </c>
       <c r="G69">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H69">
         <v>1000</v>
@@ -18139,7 +18139,7 @@
         <v>0.38600000000000001</v>
       </c>
       <c r="G70">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H70">
         <v>1000</v>
@@ -18192,7 +18192,7 @@
         <v>0.61899999999999999</v>
       </c>
       <c r="G71">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H71">
         <v>1000</v>
@@ -18245,7 +18245,7 @@
         <v>0.32700000000000001</v>
       </c>
       <c r="G72">
-        <v>0.47178196831064489</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H72">
         <v>1000</v>
@@ -18298,7 +18298,7 @@
         <v>0.72799999999999998</v>
       </c>
       <c r="G73">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H73">
         <v>1000</v>
@@ -18351,7 +18351,7 @@
         <v>0.76970000000000005</v>
       </c>
       <c r="G74">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H74">
         <v>999.99999999999989</v>
@@ -18404,7 +18404,7 @@
         <v>0.45539999999999997</v>
       </c>
       <c r="G75">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H75">
         <v>1000</v>
@@ -18457,7 +18457,7 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="G76">
-        <v>0.48476679312653426</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H76">
         <v>1150</v>
@@ -18510,7 +18510,7 @@
         <v>0.38200000000000001</v>
       </c>
       <c r="G77">
-        <v>0.47178196831064495</v>
+        <v>0.39784999999999998</v>
       </c>
       <c r="H77">
         <v>1000</v>
@@ -18563,7 +18563,7 @@
         <v>0.2475</v>
       </c>
       <c r="G78">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H78">
         <v>1150</v>
@@ -18616,7 +18616,7 @@
         <v>0.93240000000000001</v>
       </c>
       <c r="G79">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H79">
         <v>1000</v>
@@ -18669,7 +18669,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G80">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H80">
         <v>1000</v>
@@ -18722,7 +18722,7 @@
         <v>1.1319000000000001</v>
       </c>
       <c r="G81">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H81">
         <v>999.99999999999989</v>
@@ -18775,7 +18775,7 @@
         <v>0.495</v>
       </c>
       <c r="G82">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H82">
         <v>1000</v>
@@ -18828,7 +18828,7 @@
         <v>0.59</v>
       </c>
       <c r="G83">
-        <v>0.47178196831064489</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H83">
         <v>1000</v>
@@ -18881,7 +18881,7 @@
         <v>0.59</v>
       </c>
       <c r="G84">
-        <v>0.47178196831064489</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H84">
         <v>1000</v>
@@ -18934,7 +18934,7 @@
         <v>0.495</v>
       </c>
       <c r="G85">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H85">
         <v>1000</v>
@@ -18987,7 +18987,7 @@
         <v>1.1513</v>
       </c>
       <c r="G86">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H86">
         <v>1000</v>
@@ -19040,7 +19040,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="G87">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H87">
         <v>1150</v>
@@ -19093,7 +19093,7 @@
         <v>0.36260000000000003</v>
       </c>
       <c r="G88">
-        <v>0.45446886855612584</v>
+        <v>0.38324999999999998</v>
       </c>
       <c r="H88">
         <v>999.99999999999989</v>
@@ -19146,7 +19146,7 @@
         <v>0.9</v>
       </c>
       <c r="G89">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H89">
         <v>1000</v>
@@ -19199,7 +19199,7 @@
         <v>0.26600000000000001</v>
       </c>
       <c r="G90">
-        <v>0.4847667931265342</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H90">
         <v>1150</v>
@@ -19252,7 +19252,7 @@
         <v>0.505</v>
       </c>
       <c r="G91">
-        <v>0.45446886855612584</v>
+        <v>0.38324999999999998</v>
       </c>
       <c r="H91">
         <v>1000</v>
@@ -19305,7 +19305,7 @@
         <v>0.5</v>
       </c>
       <c r="G92">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H92">
         <v>1000</v>
@@ -19358,7 +19358,7 @@
         <v>0.495</v>
       </c>
       <c r="G93">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H93">
         <v>1000</v>
@@ -19411,7 +19411,7 @@
         <v>0.495</v>
       </c>
       <c r="G94">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H94">
         <v>1000</v>
@@ -19464,7 +19464,7 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="G95">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H95">
         <v>1000</v>
@@ -19517,7 +19517,7 @@
         <v>0.54900000000000004</v>
       </c>
       <c r="G96">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H96">
         <v>1000</v>
@@ -19570,7 +19570,7 @@
         <v>0.56459999999999999</v>
       </c>
       <c r="G97">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H97">
         <v>1000</v>
@@ -19623,7 +19623,7 @@
         <v>0.252</v>
       </c>
       <c r="G98">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H98">
         <v>1150</v>
@@ -19676,7 +19676,7 @@
         <v>0.252</v>
       </c>
       <c r="G99">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H99">
         <v>1150</v>
@@ -19729,7 +19729,7 @@
         <v>0.65600000000000003</v>
       </c>
       <c r="G100">
-        <v>0.51939299263557237</v>
+        <v>0.43799999999999994</v>
       </c>
       <c r="H100">
         <v>1000</v>
@@ -19782,7 +19782,7 @@
         <v>0.32400000000000001</v>
       </c>
       <c r="G101">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H101">
         <v>1000</v>
@@ -19835,7 +19835,7 @@
         <v>0.57699999999999996</v>
       </c>
       <c r="G102">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H102">
         <v>1000</v>
@@ -19888,7 +19888,7 @@
         <v>0.57799999999999996</v>
       </c>
       <c r="G103">
-        <v>0.47178196831064501</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H103">
         <v>1000</v>
@@ -19941,7 +19941,7 @@
         <v>0.54800000000000004</v>
       </c>
       <c r="G104">
-        <v>0.47178196831064501</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H104">
         <v>1000</v>
@@ -19994,7 +19994,7 @@
         <v>0.54800000000000004</v>
       </c>
       <c r="G105">
-        <v>0.47178196831064501</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H105">
         <v>1000</v>
@@ -20047,7 +20047,7 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="G106">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H106">
         <v>1000</v>
@@ -20100,7 +20100,7 @@
         <v>0.3</v>
       </c>
       <c r="G107">
-        <v>0.4847667931265342</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H107">
         <v>1150</v>
@@ -20153,7 +20153,7 @@
         <v>0.252</v>
       </c>
       <c r="G108">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H108">
         <v>1150</v>
@@ -20206,7 +20206,7 @@
         <v>0.252</v>
       </c>
       <c r="G109">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H109">
         <v>1150</v>
@@ -20259,7 +20259,7 @@
         <v>0.58950000000000002</v>
       </c>
       <c r="G110">
-        <v>0.47178196831064501</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H110">
         <v>1000</v>
@@ -20312,7 +20312,7 @@
         <v>0.58950000000000002</v>
       </c>
       <c r="G111">
-        <v>0.47178196831064501</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H111">
         <v>1000</v>
@@ -20365,7 +20365,7 @@
         <v>0.53700000000000003</v>
       </c>
       <c r="G112">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H112">
         <v>1000</v>
@@ -20418,7 +20418,7 @@
         <v>0.625</v>
       </c>
       <c r="G113">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H113">
         <v>1000</v>
@@ -20471,7 +20471,7 @@
         <v>0.495</v>
       </c>
       <c r="G114">
-        <v>0.47178196831064495</v>
+        <v>0.39785000000000004</v>
       </c>
       <c r="H114">
         <v>1000</v>
@@ -20524,7 +20524,7 @@
         <v>0.27789999999999998</v>
       </c>
       <c r="G115">
-        <v>0.50207989288105326</v>
+        <v>0.42339999999999994</v>
       </c>
       <c r="H115">
         <v>1150</v>
@@ -20577,7 +20577,7 @@
         <v>0.28299999999999997</v>
       </c>
       <c r="G116">
-        <v>0.4847667931265342</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H116">
         <v>1150</v>
@@ -20630,7 +20630,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="G117">
-        <v>0.48476679312653426</v>
+        <v>0.40880000000000005</v>
       </c>
       <c r="H117">
         <v>1150</v>
@@ -20683,7 +20683,7 @@
         <v>0.26500000000000001</v>
       </c>
       <c r="G118">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H118">
         <v>1150</v>
@@ -20736,7 +20736,7 @@
         <v>0.248</v>
       </c>
       <c r="G119">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H119">
         <v>1150</v>
@@ -20789,7 +20789,7 @@
         <v>0.26200000000000001</v>
       </c>
       <c r="G120">
-        <v>0.45014059361749609</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="H120">
         <v>1150</v>
@@ -20842,7 +20842,7 @@
         <v>0.37139999999999995</v>
       </c>
       <c r="G121">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H121">
         <v>1000.0000000000001</v>
@@ -20895,7 +20895,7 @@
         <v>0.34100000000000003</v>
       </c>
       <c r="G122">
-        <v>0.51939299263557237</v>
+        <v>0.438</v>
       </c>
       <c r="H122">
         <v>1000</v>
@@ -20948,7 +20948,7 @@
         <v>0.45850000000000002</v>
       </c>
       <c r="G123">
-        <v>0.50207989288105326</v>
+        <v>0.4234</v>
       </c>
       <c r="H123">
         <v>1000</v>
@@ -21001,7 +21001,7 @@
         <v>0.05</v>
       </c>
       <c r="G124">
-        <v>0.22074202187011827</v>
+        <v>0.18615000000000001</v>
       </c>
       <c r="H124">
         <v>1080</v>
@@ -21054,7 +21054,7 @@
         <v>0.17100000000000001</v>
       </c>
       <c r="G125">
-        <v>0.22939857174737782</v>
+        <v>0.19345000000000001</v>
       </c>
       <c r="H125">
         <v>919.99999999999989</v>
@@ -21107,7 +21107,7 @@
         <v>5.96E-2</v>
       </c>
       <c r="G126">
-        <v>0.25103994644052663</v>
+        <v>0.21169999999999997</v>
       </c>
       <c r="H126">
         <v>919.99999999999989</v>
@@ -21160,7 +21160,7 @@
         <v>0.3</v>
       </c>
       <c r="G127">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H127">
         <v>919.99999999999977</v>
@@ -21213,7 +21213,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G128">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H128">
         <v>919.99999999999989</v>
@@ -21266,7 +21266,7 @@
         <v>0.2</v>
       </c>
       <c r="G129">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H129">
         <v>919.99999999999989</v>
@@ -21319,7 +21319,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G130">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H130">
         <v>919.99999999999989</v>
@@ -21372,7 +21372,7 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="G131">
-        <v>0.2770095960723053</v>
+        <v>0.2336</v>
       </c>
       <c r="H131">
         <v>919.99999999999989</v>
@@ -21425,7 +21425,7 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="G132">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H132">
         <v>919.99999999999989</v>
@@ -21478,7 +21478,7 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="G133">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H133">
         <v>919.99999999999989</v>
@@ -21531,7 +21531,7 @@
         <v>0.13090000000000002</v>
       </c>
       <c r="G134">
-        <v>0.30730752064271366</v>
+        <v>0.25914999999999999</v>
       </c>
       <c r="H134">
         <v>1265</v>
@@ -21584,7 +21584,7 @@
         <v>0.22</v>
       </c>
       <c r="G135">
-        <v>0.31163579558134336</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H135">
         <v>1265</v>
@@ -21637,7 +21637,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="G136">
-        <v>0.31163579558134341</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H136">
         <v>1265</v>
@@ -21690,7 +21690,7 @@
         <v>0.3634</v>
       </c>
       <c r="G137">
-        <v>0.31163579558134341</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H137">
         <v>1100</v>
@@ -21743,7 +21743,7 @@
         <v>0.44160000000000005</v>
       </c>
       <c r="G138">
-        <v>0.31163579558134341</v>
+        <v>0.26279999999999998</v>
       </c>
       <c r="H138">
         <v>1100</v>
@@ -21796,7 +21796,7 @@
         <v>0.15</v>
       </c>
       <c r="G139">
-        <v>0.25969649631778619</v>
+        <v>0.219</v>
       </c>
       <c r="H139">
         <v>1380</v>
@@ -21849,7 +21849,7 @@
         <v>0.15</v>
       </c>
       <c r="G140">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H140">
         <v>1380</v>
@@ -21902,7 +21902,7 @@
         <v>0.94799999999999995</v>
       </c>
       <c r="G141">
-        <v>0.2770095960723053</v>
+        <v>0.23359999999999997</v>
       </c>
       <c r="H141">
         <v>1380</v>
@@ -21955,7 +21955,7 @@
         <v>0.32</v>
       </c>
       <c r="G142">
-        <v>0.2856661459495648</v>
+        <v>0.24089999999999998</v>
       </c>
       <c r="H142">
         <v>1380</v>
@@ -22008,7 +22008,7 @@
         <v>0.63970000000000005</v>
       </c>
       <c r="G143">
-        <v>0.2943226958268243</v>
+        <v>0.24819999999999998</v>
       </c>
       <c r="H143">
         <v>1380</v>
@@ -22061,7 +22061,7 @@
         <v>0.3</v>
       </c>
       <c r="G144">
-        <v>0.2770095960723053</v>
+        <v>0.2336</v>
       </c>
       <c r="H144">
         <v>1380</v>
@@ -22114,7 +22114,7 @@
         <v>0.3</v>
       </c>
       <c r="G145">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H145">
         <v>1380</v>
@@ -22167,7 +22167,7 @@
         <v>0.35</v>
       </c>
       <c r="G146">
-        <v>0.29432269582682435</v>
+        <v>0.2482</v>
       </c>
       <c r="H146">
         <v>1200</v>
@@ -22220,7 +22220,7 @@
         <v>0.35</v>
       </c>
       <c r="G147">
-        <v>0.29432269582682435</v>
+        <v>0.2482</v>
       </c>
       <c r="H147">
         <v>1200</v>
@@ -22273,7 +22273,7 @@
         <v>0.3</v>
       </c>
       <c r="G148">
-        <v>0.2770095960723053</v>
+        <v>0.2336</v>
       </c>
       <c r="H148">
         <v>1380</v>
@@ -22326,7 +22326,7 @@
         <v>0.25</v>
       </c>
       <c r="G149">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H149">
         <v>1380</v>
@@ -22379,7 +22379,7 @@
         <v>0.3</v>
       </c>
       <c r="G150">
-        <v>0.2770095960723053</v>
+        <v>0.2336</v>
       </c>
       <c r="H150">
         <v>1380</v>
@@ -22432,7 +22432,7 @@
         <v>0.3</v>
       </c>
       <c r="G151">
-        <v>0.2770095960723053</v>
+        <v>0.2336</v>
       </c>
       <c r="H151">
         <v>1380</v>
@@ -22485,7 +22485,7 @@
         <v>0.25</v>
       </c>
       <c r="G152">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H152">
         <v>1380</v>
@@ -22538,7 +22538,7 @@
         <v>0.25</v>
       </c>
       <c r="G153">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H153">
         <v>1380</v>
@@ -25359,7 +25359,7 @@
         <v>220</v>
       </c>
       <c r="P206" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="Q206" t="s">
         <v>352</v>
@@ -25412,7 +25412,7 @@
         <v>220</v>
       </c>
       <c r="P207" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="Q207" t="s">
         <v>352</v>
@@ -25659,7 +25659,7 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="G212">
-        <v>0.43282749386297698</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="H212">
         <v>1265</v>
@@ -25712,7 +25712,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="G213">
-        <v>0.20775719705422896</v>
+        <v>0.17519999999999999</v>
       </c>
       <c r="H213">
         <v>1035</v>
@@ -25765,7 +25765,7 @@
         <v>0.316</v>
       </c>
       <c r="G214">
-        <v>0.25969649631778619</v>
+        <v>0.21899999999999997</v>
       </c>
       <c r="H214">
         <v>1494.9999999999998</v>
@@ -25818,7 +25818,7 @@
         <v>0.113</v>
       </c>
       <c r="G215">
-        <v>0.25969649631778619</v>
+        <v>0.219</v>
       </c>
       <c r="H215">
         <v>1494.9999999999998</v>
@@ -25871,7 +25871,7 @@
         <v>0.48399999999999999</v>
       </c>
       <c r="G216">
-        <v>0.25969649631778619</v>
+        <v>0.21900000000000003</v>
       </c>
       <c r="H216">
         <v>1494.9999999999998</v>
@@ -25924,7 +25924,7 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="G217">
-        <v>0.26835304619504574</v>
+        <v>0.22630000000000003</v>
       </c>
       <c r="H217">
         <v>1494.9999999999998</v>
@@ -25977,7 +25977,7 @@
         <v>0.32</v>
       </c>
       <c r="G218">
-        <v>0.26835304619504574</v>
+        <v>0.2263</v>
       </c>
       <c r="H218">
         <v>1494.9999999999998</v>
@@ -25998,7 +25998,7 @@
         <v>235</v>
       </c>
       <c r="P218" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="Q218" t="s">
         <v>352</v>
@@ -26030,7 +26030,7 @@
         <v>0.32</v>
       </c>
       <c r="G219">
-        <v>0.2770095960723053</v>
+        <v>0.23359999999999997</v>
       </c>
       <c r="H219">
         <v>1494.9999999999998</v>
@@ -26051,7 +26051,7 @@
         <v>235</v>
       </c>
       <c r="P219" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="Q219" t="s">
         <v>352</v>
@@ -26083,7 +26083,7 @@
         <v>0.32300000000000001</v>
       </c>
       <c r="G220">
-        <v>0.2770095960723053</v>
+        <v>0.2336</v>
       </c>
       <c r="H220">
         <v>1300</v>
@@ -26136,7 +26136,7 @@
         <v>0.35</v>
       </c>
       <c r="G221">
-        <v>0.2856661459495648</v>
+        <v>0.2409</v>
       </c>
       <c r="H221">
         <v>1300</v>
@@ -26189,7 +26189,7 @@
         <v>0.35</v>
       </c>
       <c r="G222">
-        <v>0.2856661459495648</v>
+        <v>0.2409</v>
       </c>
       <c r="H222">
         <v>1300</v>
@@ -26242,7 +26242,7 @@
         <v>0.35</v>
       </c>
       <c r="G223">
-        <v>0.29432269582682435</v>
+        <v>0.2482</v>
       </c>
       <c r="H223">
         <v>1300</v>
@@ -26295,7 +26295,7 @@
         <v>0.35</v>
       </c>
       <c r="G224">
-        <v>0.29432269582682435</v>
+        <v>0.2482</v>
       </c>
       <c r="H224">
         <v>1300</v>
@@ -26348,7 +26348,7 @@
         <v>0.35</v>
       </c>
       <c r="G225">
-        <v>0.29432269582682435</v>
+        <v>0.2482</v>
       </c>
       <c r="H225">
         <v>1300</v>
@@ -26401,7 +26401,7 @@
         <v>0.35</v>
       </c>
       <c r="G226">
-        <v>0.29432269582682435</v>
+        <v>0.2482</v>
       </c>
       <c r="H226">
         <v>1300</v>
@@ -26454,7 +26454,7 @@
         <v>0.35</v>
       </c>
       <c r="G227">
-        <v>0.29432269582682435</v>
+        <v>0.2482</v>
       </c>
       <c r="H227">
         <v>1300</v>
@@ -26507,7 +26507,7 @@
         <v>0.35</v>
       </c>
       <c r="G228">
-        <v>0.29432269582682435</v>
+        <v>0.2482</v>
       </c>
       <c r="H228">
         <v>1300</v>
@@ -26752,7 +26752,7 @@
         <v>255</v>
       </c>
       <c r="P232" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="Q232" t="s">
         <v>352</v>
@@ -26808,7 +26808,7 @@
         <v>255</v>
       </c>
       <c r="P233" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="Q233" t="s">
         <v>352</v>
@@ -26920,7 +26920,7 @@
         <v>259</v>
       </c>
       <c r="P235" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="Q235" t="s">
         <v>352</v>
@@ -26976,7 +26976,7 @@
         <v>259</v>
       </c>
       <c r="P236" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="Q236" t="s">
         <v>352</v>
@@ -29552,7 +29552,7 @@
         <v>322</v>
       </c>
       <c r="P282" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="Q282" t="s">
         <v>352</v>
@@ -29608,7 +29608,7 @@
         <v>322</v>
       </c>
       <c r="P283" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="Q283" t="s">
         <v>352</v>
@@ -34116,7 +34116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A98DE3F-34DF-4309-86E8-BB6406271A70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7100F3FA-7117-4459-ACA2-A9BCA1E80116}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_MEX/vt_vervestacks_MEX_v1.xlsx
+++ b/VerveStacks_MEX/vt_vervestacks_MEX_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40191983-6CCC-430A-B655-363F3B6A5B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0872750-8133-45EC-AFF2-C088886756AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EEB89A62-4361-4231-9A93-8D44B27AA423}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DCED2FD5-16A2-4A0D-A815-5A5FAA03A4B4}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3277,7 +3277,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE4B7F7D-D39C-4A2B-8312-121B0EBB98DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830A269C-81B5-464F-9B16-F90756ECF388}">
   <dimension ref="B9:V142"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3365,7 +3365,7 @@
         <v>16</v>
       </c>
       <c r="F11">
-        <v>7.350656160000002E-2</v>
+        <v>6.6457987200000013E-2</v>
       </c>
       <c r="G11">
         <v>3583</v>
@@ -3427,7 +3427,7 @@
         <v>16</v>
       </c>
       <c r="F12">
-        <v>7.323360000000001E-2</v>
+        <v>6.6211200000000026E-2</v>
       </c>
       <c r="G12">
         <v>3583</v>
@@ -3489,7 +3489,7 @@
         <v>16</v>
       </c>
       <c r="F13">
-        <v>7.323360000000001E-2</v>
+        <v>6.6211200000000026E-2</v>
       </c>
       <c r="G13">
         <v>3583</v>
@@ -3551,7 +3551,7 @@
         <v>16</v>
       </c>
       <c r="F14">
-        <v>7.323360000000001E-2</v>
+        <v>6.6211200000000026E-2</v>
       </c>
       <c r="G14">
         <v>3583</v>
@@ -3613,7 +3613,7 @@
         <v>16</v>
       </c>
       <c r="F15">
-        <v>7.323360000000001E-2</v>
+        <v>6.6211200000000026E-2</v>
       </c>
       <c r="G15">
         <v>3583</v>
@@ -3675,7 +3675,7 @@
         <v>16</v>
       </c>
       <c r="F16">
-        <v>7.9891200000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G16">
         <v>3583</v>
@@ -3737,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="F17">
-        <v>7.9891200000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G17">
         <v>3583</v>
@@ -3799,7 +3799,7 @@
         <v>16</v>
       </c>
       <c r="F18">
-        <v>7.9891200000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G18">
         <v>3583</v>
@@ -3861,7 +3861,7 @@
         <v>16</v>
       </c>
       <c r="F19">
-        <v>7.9891200000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G19">
         <v>3583</v>
@@ -3923,7 +3923,7 @@
         <v>16</v>
       </c>
       <c r="F20">
-        <v>7.9891200000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G20">
         <v>3583</v>
@@ -3985,7 +3985,7 @@
         <v>16</v>
       </c>
       <c r="F21">
-        <v>7.9891200000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G21">
         <v>3583</v>
@@ -4047,7 +4047,7 @@
         <v>16</v>
       </c>
       <c r="F22">
-        <v>7.9891200000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G22">
         <v>3583</v>
@@ -4109,7 +4109,7 @@
         <v>16</v>
       </c>
       <c r="F23">
-        <v>7.9891200000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G23">
         <v>3583</v>
@@ -4171,7 +4171,7 @@
         <v>16</v>
       </c>
       <c r="F24">
-        <v>7.9891200000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G24">
         <v>3583</v>
@@ -4233,7 +4233,7 @@
         <v>16</v>
       </c>
       <c r="F25">
-        <v>7.9891200000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G25">
         <v>3583</v>
@@ -4295,7 +4295,7 @@
         <v>16</v>
       </c>
       <c r="F26">
-        <v>0.20011490000000001</v>
+        <v>0.18092580000000005</v>
       </c>
       <c r="G26">
         <v>2445</v>
@@ -4357,7 +4357,7 @@
         <v>16</v>
       </c>
       <c r="F27">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G27">
         <v>1365</v>
@@ -4419,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="F28">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G28">
         <v>1365</v>
@@ -4481,7 +4481,7 @@
         <v>16</v>
       </c>
       <c r="F29">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G29">
         <v>1365</v>
@@ -4543,7 +4543,7 @@
         <v>16</v>
       </c>
       <c r="F30">
-        <v>0.370475</v>
+        <v>0.33494999999999991</v>
       </c>
       <c r="G30">
         <v>1365</v>
@@ -4605,7 +4605,7 @@
         <v>16</v>
       </c>
       <c r="F31">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G31">
         <v>1365</v>
@@ -4667,7 +4667,7 @@
         <v>16</v>
       </c>
       <c r="F32">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G32">
         <v>1365</v>
@@ -4729,7 +4729,7 @@
         <v>16</v>
       </c>
       <c r="F33">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G33">
         <v>1365</v>
@@ -4791,7 +4791,7 @@
         <v>16</v>
       </c>
       <c r="F34">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G34">
         <v>1365</v>
@@ -4853,7 +4853,7 @@
         <v>16</v>
       </c>
       <c r="F35">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G35">
         <v>1365</v>
@@ -4915,7 +4915,7 @@
         <v>16</v>
       </c>
       <c r="F36">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G36">
         <v>1365</v>
@@ -4977,7 +4977,7 @@
         <v>16</v>
       </c>
       <c r="F37">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G37">
         <v>1365</v>
@@ -5039,7 +5039,7 @@
         <v>16</v>
       </c>
       <c r="F38">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G38">
         <v>1365</v>
@@ -5101,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="F39">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G39">
         <v>1365</v>
@@ -5163,7 +5163,7 @@
         <v>16</v>
       </c>
       <c r="F40">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G40">
         <v>1365</v>
@@ -5225,7 +5225,7 @@
         <v>16</v>
       </c>
       <c r="F41">
-        <v>0.35770000000000002</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G41">
         <v>1365</v>
@@ -5287,7 +5287,7 @@
         <v>16</v>
       </c>
       <c r="F42">
-        <v>0.35770000000000002</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G42">
         <v>1365</v>
@@ -5349,7 +5349,7 @@
         <v>16</v>
       </c>
       <c r="F43">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G43">
         <v>1365</v>
@@ -5411,7 +5411,7 @@
         <v>16</v>
       </c>
       <c r="F44">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G44">
         <v>1365</v>
@@ -5473,7 +5473,7 @@
         <v>16</v>
       </c>
       <c r="F45">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G45">
         <v>1365</v>
@@ -5535,7 +5535,7 @@
         <v>16</v>
       </c>
       <c r="F46">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G46">
         <v>1365</v>
@@ -5597,7 +5597,7 @@
         <v>16</v>
       </c>
       <c r="F47">
-        <v>0.33534375</v>
+        <v>0.3031875</v>
       </c>
       <c r="G47">
         <v>1365</v>
@@ -5659,7 +5659,7 @@
         <v>16</v>
       </c>
       <c r="F48">
-        <v>0.28743750000000001</v>
+        <v>0.25987500000000002</v>
       </c>
       <c r="G48">
         <v>1365</v>
@@ -5721,7 +5721,7 @@
         <v>16</v>
       </c>
       <c r="F49">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G49">
         <v>1365</v>
@@ -5783,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="F50">
-        <v>0.33214999999999995</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G50">
         <v>1365</v>
@@ -5845,7 +5845,7 @@
         <v>16</v>
       </c>
       <c r="F51">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999991</v>
       </c>
       <c r="G51">
         <v>1365</v>
@@ -5907,7 +5907,7 @@
         <v>16</v>
       </c>
       <c r="F52">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G52">
         <v>1365</v>
@@ -5969,7 +5969,7 @@
         <v>16</v>
       </c>
       <c r="F53">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G53">
         <v>1365</v>
@@ -6031,7 +6031,7 @@
         <v>16</v>
       </c>
       <c r="F54">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G54">
         <v>1365</v>
@@ -6093,7 +6093,7 @@
         <v>16</v>
       </c>
       <c r="F55">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G55">
         <v>1365</v>
@@ -6155,7 +6155,7 @@
         <v>16</v>
       </c>
       <c r="F56">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G56">
         <v>1365</v>
@@ -6217,7 +6217,7 @@
         <v>16</v>
       </c>
       <c r="F57">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G57">
         <v>1365</v>
@@ -6279,7 +6279,7 @@
         <v>16</v>
       </c>
       <c r="F58">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G58">
         <v>1365</v>
@@ -6341,7 +6341,7 @@
         <v>16</v>
       </c>
       <c r="F59">
-        <v>0.35770000000000002</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G59">
         <v>1365</v>
@@ -6403,7 +6403,7 @@
         <v>16</v>
       </c>
       <c r="F60">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G60">
         <v>1365</v>
@@ -6465,7 +6465,7 @@
         <v>16</v>
       </c>
       <c r="F61">
-        <v>0.33214999999999995</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G61">
         <v>1365</v>
@@ -6527,7 +6527,7 @@
         <v>16</v>
       </c>
       <c r="F62">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G62">
         <v>1365</v>
@@ -6589,7 +6589,7 @@
         <v>16</v>
       </c>
       <c r="F63">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G63">
         <v>1365</v>
@@ -6651,7 +6651,7 @@
         <v>16</v>
       </c>
       <c r="F64">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G64">
         <v>1365</v>
@@ -6713,7 +6713,7 @@
         <v>16</v>
       </c>
       <c r="F65">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G65">
         <v>1365</v>
@@ -6775,7 +6775,7 @@
         <v>16</v>
       </c>
       <c r="F66">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G66">
         <v>1365</v>
@@ -6837,7 +6837,7 @@
         <v>16</v>
       </c>
       <c r="F67">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G67">
         <v>1365</v>
@@ -6899,7 +6899,7 @@
         <v>16</v>
       </c>
       <c r="F68">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G68">
         <v>1365</v>
@@ -6961,7 +6961,7 @@
         <v>16</v>
       </c>
       <c r="F69">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G69">
         <v>1365</v>
@@ -7023,7 +7023,7 @@
         <v>16</v>
       </c>
       <c r="F70">
-        <v>0.33214999999999995</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G70">
         <v>1365</v>
@@ -7085,7 +7085,7 @@
         <v>16</v>
       </c>
       <c r="F71">
-        <v>0.33534375</v>
+        <v>0.3031875</v>
       </c>
       <c r="G71">
         <v>1365</v>
@@ -7147,7 +7147,7 @@
         <v>16</v>
       </c>
       <c r="F72">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G72">
         <v>1365</v>
@@ -7209,7 +7209,7 @@
         <v>16</v>
       </c>
       <c r="F73">
-        <v>0.35770000000000002</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G73">
         <v>1365</v>
@@ -7271,7 +7271,7 @@
         <v>16</v>
       </c>
       <c r="F74">
-        <v>0.33534375</v>
+        <v>0.3031875</v>
       </c>
       <c r="G74">
         <v>1365</v>
@@ -7333,7 +7333,7 @@
         <v>16</v>
       </c>
       <c r="F75">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G75">
         <v>1365</v>
@@ -7395,7 +7395,7 @@
         <v>16</v>
       </c>
       <c r="F76">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G76">
         <v>1365</v>
@@ -7457,7 +7457,7 @@
         <v>16</v>
       </c>
       <c r="F77">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G77">
         <v>1365</v>
@@ -7519,7 +7519,7 @@
         <v>16</v>
       </c>
       <c r="F78">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G78">
         <v>1365</v>
@@ -7581,7 +7581,7 @@
         <v>16</v>
       </c>
       <c r="F79">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G79">
         <v>1365</v>
@@ -7643,7 +7643,7 @@
         <v>16</v>
       </c>
       <c r="F80">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G80">
         <v>1365</v>
@@ -7705,7 +7705,7 @@
         <v>16</v>
       </c>
       <c r="F81">
-        <v>0.33214999999999995</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G81">
         <v>1365</v>
@@ -7767,7 +7767,7 @@
         <v>16</v>
       </c>
       <c r="F82">
-        <v>0.33214999999999995</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G82">
         <v>1365</v>
@@ -7829,7 +7829,7 @@
         <v>16</v>
       </c>
       <c r="F83">
-        <v>0.38324999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G83">
         <v>1365</v>
@@ -7891,7 +7891,7 @@
         <v>16</v>
       </c>
       <c r="F84">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G84">
         <v>1365</v>
@@ -7953,7 +7953,7 @@
         <v>16</v>
       </c>
       <c r="F85">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G85">
         <v>1365</v>
@@ -8015,7 +8015,7 @@
         <v>16</v>
       </c>
       <c r="F86">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G86">
         <v>1365</v>
@@ -8077,7 +8077,7 @@
         <v>16</v>
       </c>
       <c r="F87">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G87">
         <v>1365</v>
@@ -8139,7 +8139,7 @@
         <v>16</v>
       </c>
       <c r="F88">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G88">
         <v>1365</v>
@@ -8201,7 +8201,7 @@
         <v>16</v>
       </c>
       <c r="F89">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999991</v>
       </c>
       <c r="G89">
         <v>1365</v>
@@ -8263,7 +8263,7 @@
         <v>16</v>
       </c>
       <c r="F90">
-        <v>0.35770000000000002</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G90">
         <v>1365</v>
@@ -8325,7 +8325,7 @@
         <v>16</v>
       </c>
       <c r="F91">
-        <v>0.33214999999999995</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G91">
         <v>1365</v>
@@ -8387,7 +8387,7 @@
         <v>16</v>
       </c>
       <c r="F92">
-        <v>0.33214999999999995</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G92">
         <v>1365</v>
@@ -8449,7 +8449,7 @@
         <v>16</v>
       </c>
       <c r="F93">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G93">
         <v>1365</v>
@@ -8511,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="F94">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G94">
         <v>1365</v>
@@ -8573,7 +8573,7 @@
         <v>16</v>
       </c>
       <c r="F95">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G95">
         <v>1365</v>
@@ -8635,7 +8635,7 @@
         <v>16</v>
       </c>
       <c r="F96">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G96">
         <v>1365</v>
@@ -8697,7 +8697,7 @@
         <v>16</v>
       </c>
       <c r="F97">
-        <v>0.34811875000000003</v>
+        <v>0.3147375</v>
       </c>
       <c r="G97">
         <v>1365</v>
@@ -8759,7 +8759,7 @@
         <v>16</v>
       </c>
       <c r="F98">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G98">
         <v>1365</v>
@@ -8821,7 +8821,7 @@
         <v>16</v>
       </c>
       <c r="F99">
-        <v>0.35770000000000002</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G99">
         <v>1365</v>
@@ -8883,7 +8883,7 @@
         <v>16</v>
       </c>
       <c r="F100">
-        <v>0.35770000000000002</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G100">
         <v>1365</v>
@@ -8945,7 +8945,7 @@
         <v>16</v>
       </c>
       <c r="F101">
-        <v>0.33214999999999995</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G101">
         <v>1365</v>
@@ -9007,7 +9007,7 @@
         <v>16</v>
       </c>
       <c r="F102">
-        <v>0.33214999999999995</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G102">
         <v>1365</v>
@@ -9069,7 +9069,7 @@
         <v>16</v>
       </c>
       <c r="F103">
-        <v>0.33214999999999995</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G103">
         <v>1365</v>
@@ -9131,7 +9131,7 @@
         <v>16</v>
       </c>
       <c r="F104">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G104">
         <v>1365</v>
@@ -9193,7 +9193,7 @@
         <v>16</v>
       </c>
       <c r="F105">
-        <v>0.38325000000000004</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G105">
         <v>1365</v>
@@ -9255,7 +9255,7 @@
         <v>16</v>
       </c>
       <c r="F106">
-        <v>0.370475</v>
+        <v>0.33494999999999991</v>
       </c>
       <c r="G106">
         <v>1365</v>
@@ -9317,7 +9317,7 @@
         <v>16</v>
       </c>
       <c r="F107">
-        <v>0.37047499999999994</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G107">
         <v>1365</v>
@@ -9350,7 +9350,7 @@
         <v>14</v>
       </c>
       <c r="R107" t="s">
-        <v>830</v>
+        <v>926</v>
       </c>
       <c r="S107" t="s">
         <v>351</v>
@@ -9379,7 +9379,7 @@
         <v>16</v>
       </c>
       <c r="F108">
-        <v>0.19801250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G108">
         <v>1365</v>
@@ -9412,7 +9412,7 @@
         <v>14</v>
       </c>
       <c r="R108" t="s">
-        <v>926</v>
+        <v>830</v>
       </c>
       <c r="S108" t="s">
         <v>351</v>
@@ -9441,7 +9441,7 @@
         <v>16</v>
       </c>
       <c r="F109">
-        <v>0.19801250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G109">
         <v>1365</v>
@@ -9503,7 +9503,7 @@
         <v>16</v>
       </c>
       <c r="F110">
-        <v>0.20440000000000003</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G110">
         <v>1365</v>
@@ -9565,7 +9565,7 @@
         <v>16</v>
       </c>
       <c r="F111">
-        <v>0.22994999999999999</v>
+        <v>0.2079</v>
       </c>
       <c r="G111">
         <v>1365</v>
@@ -9627,7 +9627,7 @@
         <v>16</v>
       </c>
       <c r="F112">
-        <v>0.22994999999999999</v>
+        <v>0.20790000000000003</v>
       </c>
       <c r="G112">
         <v>1365</v>
@@ -9689,7 +9689,7 @@
         <v>16</v>
       </c>
       <c r="F113">
-        <v>0.22994999999999999</v>
+        <v>0.20790000000000003</v>
       </c>
       <c r="G113">
         <v>1365</v>
@@ -9751,7 +9751,7 @@
         <v>16</v>
       </c>
       <c r="F114">
-        <v>0.20440000000000003</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G114">
         <v>1365</v>
@@ -9784,7 +9784,7 @@
         <v>14</v>
       </c>
       <c r="R114" t="s">
-        <v>830</v>
+        <v>926</v>
       </c>
       <c r="S114" t="s">
         <v>351</v>
@@ -9813,7 +9813,7 @@
         <v>16</v>
       </c>
       <c r="F115">
-        <v>0.19801250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G115">
         <v>1365</v>
@@ -9846,7 +9846,7 @@
         <v>14</v>
       </c>
       <c r="R115" t="s">
-        <v>926</v>
+        <v>830</v>
       </c>
       <c r="S115" t="s">
         <v>351</v>
@@ -9875,7 +9875,7 @@
         <v>16</v>
       </c>
       <c r="F116">
-        <v>0.21717500000000001</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G116">
         <v>1365</v>
@@ -9937,7 +9937,7 @@
         <v>16</v>
       </c>
       <c r="F117">
-        <v>0.21717500000000001</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G117">
         <v>1365</v>
@@ -9999,7 +9999,7 @@
         <v>16</v>
       </c>
       <c r="F118">
-        <v>0.20440000000000003</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G118">
         <v>1365</v>
@@ -10061,7 +10061,7 @@
         <v>16</v>
       </c>
       <c r="F119">
-        <v>0.19801250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G119">
         <v>1365</v>
@@ -10123,7 +10123,7 @@
         <v>16</v>
       </c>
       <c r="F120">
-        <v>0.20440000000000003</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G120">
         <v>1365</v>
@@ -10185,7 +10185,7 @@
         <v>16</v>
       </c>
       <c r="F121">
-        <v>0.20440000000000003</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G121">
         <v>1365</v>
@@ -10247,7 +10247,7 @@
         <v>16</v>
       </c>
       <c r="F122">
-        <v>0.19801250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G122">
         <v>1365</v>
@@ -10309,7 +10309,7 @@
         <v>16</v>
       </c>
       <c r="F123">
-        <v>0.19801250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G123">
         <v>1365</v>
@@ -10371,7 +10371,7 @@
         <v>16</v>
       </c>
       <c r="F124">
-        <v>0.21717499999999998</v>
+        <v>0.19634999999999997</v>
       </c>
       <c r="G124">
         <v>1365</v>
@@ -10681,7 +10681,7 @@
         <v>16</v>
       </c>
       <c r="F129">
-        <v>0.31937500000000002</v>
+        <v>0.28875000000000001</v>
       </c>
       <c r="G129">
         <v>1365</v>
@@ -10743,7 +10743,7 @@
         <v>16</v>
       </c>
       <c r="F130">
-        <v>0.15329999999999999</v>
+        <v>0.1386</v>
       </c>
       <c r="G130">
         <v>1365</v>
@@ -10805,7 +10805,7 @@
         <v>16</v>
       </c>
       <c r="F131">
-        <v>0.20440000000000003</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G131">
         <v>1365</v>
@@ -10867,7 +10867,7 @@
         <v>16</v>
       </c>
       <c r="F132">
-        <v>0.21078749999999999</v>
+        <v>0.19057500000000002</v>
       </c>
       <c r="G132">
         <v>1365</v>
@@ -10929,7 +10929,7 @@
         <v>16</v>
       </c>
       <c r="F133">
-        <v>0.21078749999999999</v>
+        <v>0.19057500000000002</v>
       </c>
       <c r="G133">
         <v>1365</v>
@@ -10991,7 +10991,7 @@
         <v>16</v>
       </c>
       <c r="F134">
-        <v>0.21717500000000001</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G134">
         <v>1365</v>
@@ -11053,7 +11053,7 @@
         <v>16</v>
       </c>
       <c r="F135">
-        <v>0.21717500000000001</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G135">
         <v>1365</v>
@@ -11115,7 +11115,7 @@
         <v>16</v>
       </c>
       <c r="F136">
-        <v>0.21717500000000001</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G136">
         <v>1365</v>
@@ -11177,7 +11177,7 @@
         <v>16</v>
       </c>
       <c r="F137">
-        <v>0.21717500000000001</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G137">
         <v>1365</v>
@@ -11239,7 +11239,7 @@
         <v>16</v>
       </c>
       <c r="F138">
-        <v>0.21717500000000001</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G138">
         <v>1365</v>
@@ -11301,7 +11301,7 @@
         <v>16</v>
       </c>
       <c r="F139">
-        <v>0.21717500000000001</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G139">
         <v>1365</v>
@@ -11363,7 +11363,7 @@
         <v>16</v>
       </c>
       <c r="F140">
-        <v>0.20439999999999997</v>
+        <v>0.18479999999999999</v>
       </c>
       <c r="G140">
         <v>1365</v>
@@ -11469,7 +11469,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C80F9F1-8F48-48CB-8B03-B9E221CBDC62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47DE23D8-70B0-4CDB-A9DA-5488C73ABF14}">
   <dimension ref="B9:V81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15924,7 +15924,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DBE526-887F-4C32-BD49-C2CEC11E457C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AAA8B7-3DDF-4D6E-98AE-DEFD884252C8}">
   <dimension ref="B9:V402"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16018,7 +16018,7 @@
         <v>0.08</v>
       </c>
       <c r="H11">
-        <v>0.219</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I11">
         <v>4725</v>
@@ -16077,7 +16077,7 @@
         <v>0.14299999999999999</v>
       </c>
       <c r="H12">
-        <v>0.219</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I12">
         <v>4725</v>
@@ -16136,7 +16136,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="H13">
-        <v>0.219</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I13">
         <v>4725</v>
@@ -16195,7 +16195,7 @@
         <v>0.05</v>
       </c>
       <c r="H14">
-        <v>0.21899999999999997</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I14">
         <v>4725</v>
@@ -16254,7 +16254,7 @@
         <v>0.57621000000000011</v>
       </c>
       <c r="H15">
-        <v>0.2555</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="I15">
         <v>3500</v>
@@ -16313,7 +16313,7 @@
         <v>1.9999999999997797E-3</v>
       </c>
       <c r="H16">
-        <v>0.24179790000000001</v>
+        <v>0.21861180000000002</v>
       </c>
       <c r="L16">
         <v>33</v>
@@ -16363,7 +16363,7 @@
         <v>0.3</v>
       </c>
       <c r="H17">
-        <v>0.24089999999999998</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I17">
         <v>2300</v>
@@ -16422,7 +16422,7 @@
         <v>0.3</v>
       </c>
       <c r="H18">
-        <v>0.24089999999999998</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I18">
         <v>2300</v>
@@ -16481,7 +16481,7 @@
         <v>0.3</v>
       </c>
       <c r="H19">
-        <v>0.24089999999999998</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I19">
         <v>2300</v>
@@ -16540,7 +16540,7 @@
         <v>0.3</v>
       </c>
       <c r="H20">
-        <v>0.24089999999999998</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I20">
         <v>2300</v>
@@ -16599,7 +16599,7 @@
         <v>0.35</v>
       </c>
       <c r="H21">
-        <v>0.26279999999999998</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I21">
         <v>2000</v>
@@ -16658,7 +16658,7 @@
         <v>0.35</v>
       </c>
       <c r="H22">
-        <v>0.26279999999999998</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I22">
         <v>2000</v>
@@ -16717,7 +16717,7 @@
         <v>0.35</v>
       </c>
       <c r="H23">
-        <v>0.26279999999999998</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I23">
         <v>2000</v>
@@ -16776,7 +16776,7 @@
         <v>0.35</v>
       </c>
       <c r="H24">
-        <v>0.26279999999999998</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I24">
         <v>2000</v>
@@ -16835,7 +16835,7 @@
         <v>0.35</v>
       </c>
       <c r="H25">
-        <v>0.26279999999999998</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I25">
         <v>2000</v>
@@ -16894,7 +16894,7 @@
         <v>0.35</v>
       </c>
       <c r="H26">
-        <v>0.26279999999999998</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I26">
         <v>2000</v>
@@ -16953,7 +16953,7 @@
         <v>0.35</v>
       </c>
       <c r="H27">
-        <v>0.26279999999999998</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I27">
         <v>2000</v>
@@ -17012,7 +17012,7 @@
         <v>0.35</v>
       </c>
       <c r="H28">
-        <v>0.26279999999999998</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I28">
         <v>2000</v>
@@ -17071,7 +17071,7 @@
         <v>0.35</v>
       </c>
       <c r="H29">
-        <v>0.26279999999999998</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I29">
         <v>2000</v>
@@ -17130,7 +17130,7 @@
         <v>0.35</v>
       </c>
       <c r="H30">
-        <v>0.26279999999999998</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I30">
         <v>2000</v>
@@ -17189,7 +17189,7 @@
         <v>0.67800000000000005</v>
       </c>
       <c r="H31">
-        <v>0.28835</v>
+        <v>0.26070000000000004</v>
       </c>
       <c r="I31">
         <v>2200</v>
@@ -17248,7 +17248,7 @@
         <v>0.23980000000000001</v>
       </c>
       <c r="H32">
-        <v>0.27739999999999998</v>
+        <v>0.25080000000000002</v>
       </c>
       <c r="I32">
         <v>1150</v>
@@ -17307,7 +17307,7 @@
         <v>0.33550000000000002</v>
       </c>
       <c r="H33">
-        <v>0.36500000000000005</v>
+        <v>0.33</v>
       </c>
       <c r="I33">
         <v>1150</v>
@@ -17366,7 +17366,7 @@
         <v>0.22</v>
       </c>
       <c r="H34">
-        <v>0.36499999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="I34">
         <v>1150</v>
@@ -17425,7 +17425,7 @@
         <v>0.45200000000000001</v>
       </c>
       <c r="H35">
-        <v>0.36499999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="I35">
         <v>1150</v>
@@ -17484,7 +17484,7 @@
         <v>0.66600000000000004</v>
       </c>
       <c r="H36">
-        <v>0.36499999999999994</v>
+        <v>0.33000000000000007</v>
       </c>
       <c r="I36">
         <v>1150</v>
@@ -17543,7 +17543,7 @@
         <v>0.22700000000000001</v>
       </c>
       <c r="H37">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I37">
         <v>1150</v>
@@ -17602,7 +17602,7 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="H38">
-        <v>0.37960000000000005</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I38">
         <v>1150</v>
@@ -17661,7 +17661,7 @@
         <v>0.32300000000000001</v>
       </c>
       <c r="H39">
-        <v>0.40880000000000005</v>
+        <v>0.3696000000000001</v>
       </c>
       <c r="I39">
         <v>1150</v>
@@ -17720,7 +17720,7 @@
         <v>0.45960000000000001</v>
       </c>
       <c r="H40">
-        <v>0.40880000000000005</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I40">
         <v>1150</v>
@@ -17779,7 +17779,7 @@
         <v>0.19700000000000001</v>
       </c>
       <c r="H41">
-        <v>0.40880000000000005</v>
+        <v>0.3696000000000001</v>
       </c>
       <c r="I41">
         <v>1150</v>
@@ -17838,7 +17838,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="H42">
-        <v>0.40880000000000005</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I42">
         <v>1150</v>
@@ -17897,7 +17897,7 @@
         <v>0.15</v>
       </c>
       <c r="H43">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I43">
         <v>1150</v>
@@ -17956,7 +17956,7 @@
         <v>0.51400000000000001</v>
       </c>
       <c r="H44">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I44">
         <v>1000</v>
@@ -18015,7 +18015,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="H45">
-        <v>0.42339999999999989</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I45">
         <v>1000</v>
@@ -18074,7 +18074,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="H46">
-        <v>0.42339999999999989</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I46">
         <v>1000</v>
@@ -18133,7 +18133,7 @@
         <v>0.45850000000000002</v>
       </c>
       <c r="H47">
-        <v>0.4234</v>
+        <v>0.38279999999999992</v>
       </c>
       <c r="I47">
         <v>1000</v>
@@ -18192,7 +18192,7 @@
         <v>0.874</v>
       </c>
       <c r="H48">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I48">
         <v>1000</v>
@@ -18251,7 +18251,7 @@
         <v>0.86599999999999999</v>
       </c>
       <c r="H49">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I49">
         <v>1000</v>
@@ -18310,7 +18310,7 @@
         <v>0.878</v>
       </c>
       <c r="H50">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I50">
         <v>1000</v>
@@ -18369,7 +18369,7 @@
         <v>0.85</v>
       </c>
       <c r="H51">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I51">
         <v>1000</v>
@@ -18428,7 +18428,7 @@
         <v>0.76600000000000001</v>
       </c>
       <c r="H52">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I52">
         <v>1000</v>
@@ -18487,7 +18487,7 @@
         <v>0.39300000000000002</v>
       </c>
       <c r="H53">
-        <v>0.42339999999999989</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I53">
         <v>1000</v>
@@ -18546,7 +18546,7 @@
         <v>0.35</v>
       </c>
       <c r="H54">
-        <v>0.42339999999999989</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I54">
         <v>1000</v>
@@ -18605,7 +18605,7 @@
         <v>0.433</v>
       </c>
       <c r="H55">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I55">
         <v>1000</v>
@@ -18664,7 +18664,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="H56">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I56">
         <v>1000</v>
@@ -18723,7 +18723,7 @@
         <v>0.36399999999999999</v>
       </c>
       <c r="H57">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I57">
         <v>1000</v>
@@ -18782,7 +18782,7 @@
         <v>0.2581</v>
       </c>
       <c r="H58">
-        <v>0.40880000000000005</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I58">
         <v>1150</v>
@@ -18841,7 +18841,7 @@
         <v>0.2581</v>
       </c>
       <c r="H59">
-        <v>0.40880000000000005</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I59">
         <v>1150</v>
@@ -18900,7 +18900,7 @@
         <v>0.72699999999999998</v>
       </c>
       <c r="H60">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I60">
         <v>1000</v>
@@ -18959,7 +18959,7 @@
         <v>0.72699999999999998</v>
       </c>
       <c r="H61">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I61">
         <v>1000</v>
@@ -19018,7 +19018,7 @@
         <v>1.0680000000000001</v>
       </c>
       <c r="H62">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I62">
         <v>1000</v>
@@ -19077,7 +19077,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="H63">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I63">
         <v>1000</v>
@@ -19136,7 +19136,7 @@
         <v>0.45900000000000002</v>
       </c>
       <c r="H64">
-        <v>0.38324999999999998</v>
+        <v>0.34650000000000003</v>
       </c>
       <c r="I64">
         <v>1000</v>
@@ -19195,7 +19195,7 @@
         <v>0.378</v>
       </c>
       <c r="H65">
-        <v>0.32850000000000001</v>
+        <v>0.29700000000000004</v>
       </c>
       <c r="I65">
         <v>1000</v>
@@ -19254,7 +19254,7 @@
         <v>0.76879999999999993</v>
       </c>
       <c r="H66">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I66">
         <v>1000.0000000000001</v>
@@ -19313,7 +19313,7 @@
         <v>0.25</v>
       </c>
       <c r="H67">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I67">
         <v>1150</v>
@@ -19372,7 +19372,7 @@
         <v>0.79100000000000004</v>
       </c>
       <c r="H68">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999992</v>
       </c>
       <c r="I68">
         <v>1000</v>
@@ -19431,7 +19431,7 @@
         <v>0.77</v>
       </c>
       <c r="H69">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I69">
         <v>1000</v>
@@ -19490,7 +19490,7 @@
         <v>0.38600000000000001</v>
       </c>
       <c r="H70">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I70">
         <v>1000</v>
@@ -19549,7 +19549,7 @@
         <v>0.61899999999999999</v>
       </c>
       <c r="H71">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I71">
         <v>1000</v>
@@ -19608,7 +19608,7 @@
         <v>0.32700000000000001</v>
       </c>
       <c r="H72">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I72">
         <v>1000</v>
@@ -19667,7 +19667,7 @@
         <v>0.72799999999999998</v>
       </c>
       <c r="H73">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I73">
         <v>1000</v>
@@ -19726,7 +19726,7 @@
         <v>0.76970000000000005</v>
       </c>
       <c r="H74">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I74">
         <v>999.99999999999989</v>
@@ -19785,7 +19785,7 @@
         <v>0.45539999999999997</v>
       </c>
       <c r="H75">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I75">
         <v>1000</v>
@@ -19844,7 +19844,7 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="H76">
-        <v>0.40880000000000005</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I76">
         <v>1150</v>
@@ -19903,7 +19903,7 @@
         <v>0.38200000000000001</v>
       </c>
       <c r="H77">
-        <v>0.39784999999999998</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I77">
         <v>1000</v>
@@ -19962,7 +19962,7 @@
         <v>0.2475</v>
       </c>
       <c r="H78">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I78">
         <v>1150</v>
@@ -20021,7 +20021,7 @@
         <v>0.93240000000000001</v>
       </c>
       <c r="H79">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I79">
         <v>1000</v>
@@ -20080,7 +20080,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="H80">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I80">
         <v>1000</v>
@@ -20139,7 +20139,7 @@
         <v>1.1319000000000001</v>
       </c>
       <c r="H81">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I81">
         <v>999.99999999999989</v>
@@ -20198,7 +20198,7 @@
         <v>0.495</v>
       </c>
       <c r="H82">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I82">
         <v>1000</v>
@@ -20257,7 +20257,7 @@
         <v>0.59</v>
       </c>
       <c r="H83">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I83">
         <v>1000</v>
@@ -20316,7 +20316,7 @@
         <v>0.59</v>
       </c>
       <c r="H84">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I84">
         <v>1000</v>
@@ -20375,7 +20375,7 @@
         <v>0.495</v>
       </c>
       <c r="H85">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I85">
         <v>1000</v>
@@ -20434,7 +20434,7 @@
         <v>1.1513</v>
       </c>
       <c r="H86">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I86">
         <v>1000</v>
@@ -20493,7 +20493,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="H87">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I87">
         <v>1150</v>
@@ -20552,7 +20552,7 @@
         <v>0.36260000000000003</v>
       </c>
       <c r="H88">
-        <v>0.38324999999999998</v>
+        <v>0.34650000000000003</v>
       </c>
       <c r="I88">
         <v>999.99999999999989</v>
@@ -20611,7 +20611,7 @@
         <v>0.9</v>
       </c>
       <c r="H89">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I89">
         <v>1000</v>
@@ -20670,7 +20670,7 @@
         <v>0.26600000000000001</v>
       </c>
       <c r="H90">
-        <v>0.40880000000000005</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I90">
         <v>1150</v>
@@ -20729,7 +20729,7 @@
         <v>0.505</v>
       </c>
       <c r="H91">
-        <v>0.38324999999999998</v>
+        <v>0.34650000000000003</v>
       </c>
       <c r="I91">
         <v>1000</v>
@@ -20788,7 +20788,7 @@
         <v>0.5</v>
       </c>
       <c r="H92">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I92">
         <v>1000</v>
@@ -20847,7 +20847,7 @@
         <v>0.495</v>
       </c>
       <c r="H93">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I93">
         <v>1000</v>
@@ -20906,7 +20906,7 @@
         <v>0.495</v>
       </c>
       <c r="H94">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I94">
         <v>1000</v>
@@ -20965,7 +20965,7 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="H95">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I95">
         <v>1000</v>
@@ -21024,7 +21024,7 @@
         <v>0.54900000000000004</v>
       </c>
       <c r="H96">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I96">
         <v>1000</v>
@@ -21083,7 +21083,7 @@
         <v>0.56459999999999999</v>
       </c>
       <c r="H97">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I97">
         <v>1000</v>
@@ -21142,7 +21142,7 @@
         <v>0.252</v>
       </c>
       <c r="H98">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I98">
         <v>1150</v>
@@ -21201,7 +21201,7 @@
         <v>0.252</v>
       </c>
       <c r="H99">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I99">
         <v>1150</v>
@@ -21260,7 +21260,7 @@
         <v>0.65600000000000003</v>
       </c>
       <c r="H100">
-        <v>0.43799999999999994</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I100">
         <v>1000</v>
@@ -21319,7 +21319,7 @@
         <v>0.32400000000000001</v>
       </c>
       <c r="H101">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I101">
         <v>1000</v>
@@ -21378,7 +21378,7 @@
         <v>0.57699999999999996</v>
       </c>
       <c r="H102">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I102">
         <v>1000</v>
@@ -21437,7 +21437,7 @@
         <v>0.57799999999999996</v>
       </c>
       <c r="H103">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I103">
         <v>1000</v>
@@ -21496,7 +21496,7 @@
         <v>0.54800000000000004</v>
       </c>
       <c r="H104">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I104">
         <v>1000</v>
@@ -21555,7 +21555,7 @@
         <v>0.54800000000000004</v>
       </c>
       <c r="H105">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I105">
         <v>1000</v>
@@ -21614,7 +21614,7 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="H106">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999992</v>
       </c>
       <c r="I106">
         <v>1000</v>
@@ -21673,7 +21673,7 @@
         <v>0.3</v>
       </c>
       <c r="H107">
-        <v>0.40880000000000005</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I107">
         <v>1150</v>
@@ -21732,7 +21732,7 @@
         <v>0.252</v>
       </c>
       <c r="H108">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I108">
         <v>1150</v>
@@ -21791,7 +21791,7 @@
         <v>0.252</v>
       </c>
       <c r="H109">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I109">
         <v>1150</v>
@@ -21850,7 +21850,7 @@
         <v>0.58950000000000002</v>
       </c>
       <c r="H110">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I110">
         <v>1000</v>
@@ -21909,7 +21909,7 @@
         <v>0.58950000000000002</v>
       </c>
       <c r="H111">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I111">
         <v>1000</v>
@@ -21968,7 +21968,7 @@
         <v>0.53700000000000003</v>
       </c>
       <c r="H112">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I112">
         <v>1000</v>
@@ -22027,7 +22027,7 @@
         <v>0.625</v>
       </c>
       <c r="H113">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I113">
         <v>1000</v>
@@ -22086,7 +22086,7 @@
         <v>0.495</v>
       </c>
       <c r="H114">
-        <v>0.39785000000000004</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I114">
         <v>1000</v>
@@ -22145,7 +22145,7 @@
         <v>0.27789999999999998</v>
       </c>
       <c r="H115">
-        <v>0.42339999999999994</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I115">
         <v>1150</v>
@@ -22169,7 +22169,7 @@
         <v>14</v>
       </c>
       <c r="R115" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S115" t="s">
         <v>351</v>
@@ -22204,7 +22204,7 @@
         <v>0.28299999999999997</v>
       </c>
       <c r="H116">
-        <v>0.40880000000000005</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I116">
         <v>1150</v>
@@ -22228,7 +22228,7 @@
         <v>14</v>
       </c>
       <c r="R116" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S116" t="s">
         <v>351</v>
@@ -22263,7 +22263,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="H117">
-        <v>0.40880000000000005</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I117">
         <v>1150</v>
@@ -22322,7 +22322,7 @@
         <v>0.26500000000000001</v>
       </c>
       <c r="H118">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I118">
         <v>1150</v>
@@ -22381,7 +22381,7 @@
         <v>0.248</v>
       </c>
       <c r="H119">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I119">
         <v>1150</v>
@@ -22440,7 +22440,7 @@
         <v>0.26200000000000001</v>
       </c>
       <c r="H120">
-        <v>0.37959999999999999</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I120">
         <v>1150</v>
@@ -22499,7 +22499,7 @@
         <v>0.37139999999999995</v>
       </c>
       <c r="H121">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I121">
         <v>1000.0000000000001</v>
@@ -22558,7 +22558,7 @@
         <v>0.34100000000000003</v>
       </c>
       <c r="H122">
-        <v>0.438</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I122">
         <v>1000</v>
@@ -22617,7 +22617,7 @@
         <v>0.45850000000000002</v>
       </c>
       <c r="H123">
-        <v>0.4234</v>
+        <v>0.38279999999999992</v>
       </c>
       <c r="I123">
         <v>1000</v>
@@ -22676,7 +22676,7 @@
         <v>0.05</v>
       </c>
       <c r="H124">
-        <v>0.18615000000000001</v>
+        <v>0.16830000000000001</v>
       </c>
       <c r="I124">
         <v>1080</v>
@@ -22735,7 +22735,7 @@
         <v>0.17100000000000001</v>
       </c>
       <c r="H125">
-        <v>0.19345000000000001</v>
+        <v>0.17490000000000003</v>
       </c>
       <c r="I125">
         <v>919.99999999999989</v>
@@ -22794,7 +22794,7 @@
         <v>5.96E-2</v>
       </c>
       <c r="H126">
-        <v>0.21169999999999997</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="I126">
         <v>919.99999999999989</v>
@@ -22853,7 +22853,7 @@
         <v>0.3</v>
       </c>
       <c r="H127">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I127">
         <v>919.99999999999977</v>
@@ -22912,7 +22912,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="H128">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I128">
         <v>919.99999999999989</v>
@@ -22971,7 +22971,7 @@
         <v>0.2</v>
       </c>
       <c r="H129">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I129">
         <v>919.99999999999989</v>
@@ -23030,7 +23030,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="H130">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I130">
         <v>919.99999999999989</v>
@@ -23089,7 +23089,7 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="H131">
-        <v>0.2336</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I131">
         <v>919.99999999999989</v>
@@ -23148,7 +23148,7 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="H132">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I132">
         <v>919.99999999999989</v>
@@ -23207,7 +23207,7 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="H133">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I133">
         <v>919.99999999999989</v>
@@ -23266,7 +23266,7 @@
         <v>0.13090000000000002</v>
       </c>
       <c r="H134">
-        <v>0.25914999999999999</v>
+        <v>0.23430000000000001</v>
       </c>
       <c r="I134">
         <v>1265</v>
@@ -23325,7 +23325,7 @@
         <v>0.22</v>
       </c>
       <c r="H135">
-        <v>0.26279999999999998</v>
+        <v>0.23760000000000001</v>
       </c>
       <c r="I135">
         <v>1265</v>
@@ -23384,7 +23384,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="H136">
-        <v>0.26279999999999998</v>
+        <v>0.23760000000000003</v>
       </c>
       <c r="I136">
         <v>1265</v>
@@ -23443,7 +23443,7 @@
         <v>0.3634</v>
       </c>
       <c r="H137">
-        <v>0.26279999999999998</v>
+        <v>0.23760000000000001</v>
       </c>
       <c r="I137">
         <v>1100</v>
@@ -23502,7 +23502,7 @@
         <v>0.44160000000000005</v>
       </c>
       <c r="H138">
-        <v>0.26279999999999998</v>
+        <v>0.23760000000000003</v>
       </c>
       <c r="I138">
         <v>1100</v>
@@ -23561,7 +23561,7 @@
         <v>0.15</v>
       </c>
       <c r="H139">
-        <v>0.219</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I139">
         <v>1380</v>
@@ -23620,7 +23620,7 @@
         <v>0.15</v>
       </c>
       <c r="H140">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I140">
         <v>1380</v>
@@ -23679,7 +23679,7 @@
         <v>0.94799999999999995</v>
       </c>
       <c r="H141">
-        <v>0.23359999999999997</v>
+        <v>0.2112</v>
       </c>
       <c r="I141">
         <v>1380</v>
@@ -23738,7 +23738,7 @@
         <v>0.32</v>
       </c>
       <c r="H142">
-        <v>0.24089999999999998</v>
+        <v>0.21780000000000005</v>
       </c>
       <c r="I142">
         <v>1380</v>
@@ -23797,7 +23797,7 @@
         <v>0.63970000000000005</v>
       </c>
       <c r="H143">
-        <v>0.24819999999999998</v>
+        <v>0.22439999999999996</v>
       </c>
       <c r="I143">
         <v>1380</v>
@@ -23856,7 +23856,7 @@
         <v>0.3</v>
       </c>
       <c r="H144">
-        <v>0.2336</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I144">
         <v>1380</v>
@@ -23915,7 +23915,7 @@
         <v>0.3</v>
       </c>
       <c r="H145">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I145">
         <v>1380</v>
@@ -23974,7 +23974,7 @@
         <v>0.35</v>
       </c>
       <c r="H146">
-        <v>0.2482</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I146">
         <v>1200</v>
@@ -24033,7 +24033,7 @@
         <v>0.35</v>
       </c>
       <c r="H147">
-        <v>0.2482</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I147">
         <v>1200</v>
@@ -24092,7 +24092,7 @@
         <v>0.3</v>
       </c>
       <c r="H148">
-        <v>0.2336</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I148">
         <v>1380</v>
@@ -24151,7 +24151,7 @@
         <v>0.25</v>
       </c>
       <c r="H149">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I149">
         <v>1380</v>
@@ -24210,7 +24210,7 @@
         <v>0.3</v>
       </c>
       <c r="H150">
-        <v>0.2336</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I150">
         <v>1380</v>
@@ -24269,7 +24269,7 @@
         <v>0.3</v>
       </c>
       <c r="H151">
-        <v>0.2336</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I151">
         <v>1380</v>
@@ -24328,7 +24328,7 @@
         <v>0.25</v>
       </c>
       <c r="H152">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I152">
         <v>1380</v>
@@ -24387,7 +24387,7 @@
         <v>0.25</v>
       </c>
       <c r="H153">
-        <v>0.2263</v>
+        <v>0.2046</v>
       </c>
       <c r="I153">
         <v>1380</v>
@@ -27768,7 +27768,7 @@
         <v>14</v>
       </c>
       <c r="R210" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S210" t="s">
         <v>351</v>
@@ -27827,7 +27827,7 @@
         <v>14</v>
       </c>
       <c r="R211" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S211" t="s">
         <v>351</v>
@@ -27921,7 +27921,7 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="H213">
-        <v>0.36499999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="I213">
         <v>1265</v>
@@ -27980,7 +27980,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="H214">
-        <v>0.17519999999999999</v>
+        <v>0.15840000000000001</v>
       </c>
       <c r="I214">
         <v>1035</v>
@@ -28039,7 +28039,7 @@
         <v>0.316</v>
       </c>
       <c r="H215">
-        <v>0.21899999999999997</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I215">
         <v>1494.9999999999998</v>
@@ -28098,7 +28098,7 @@
         <v>0.113</v>
       </c>
       <c r="H216">
-        <v>0.219</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I216">
         <v>1494.9999999999998</v>
@@ -28157,7 +28157,7 @@
         <v>0.48399999999999999</v>
       </c>
       <c r="H217">
-        <v>0.21900000000000003</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I217">
         <v>1494.9999999999998</v>
@@ -28216,7 +28216,7 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="H218">
-        <v>0.22630000000000003</v>
+        <v>0.2046</v>
       </c>
       <c r="I218">
         <v>1494.9999999999998</v>
@@ -28275,7 +28275,7 @@
         <v>0.32</v>
       </c>
       <c r="H219">
-        <v>0.2263</v>
+        <v>0.20460000000000003</v>
       </c>
       <c r="I219">
         <v>1494.9999999999998</v>
@@ -28334,7 +28334,7 @@
         <v>0.32</v>
       </c>
       <c r="H220">
-        <v>0.23359999999999997</v>
+        <v>0.2112</v>
       </c>
       <c r="I220">
         <v>1494.9999999999998</v>
@@ -28393,7 +28393,7 @@
         <v>0.32300000000000001</v>
       </c>
       <c r="H221">
-        <v>0.2336</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I221">
         <v>1300</v>
@@ -28452,7 +28452,7 @@
         <v>0.35</v>
       </c>
       <c r="H222">
-        <v>0.2409</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I222">
         <v>1300</v>
@@ -28476,7 +28476,7 @@
         <v>14</v>
       </c>
       <c r="R222" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S222" t="s">
         <v>351</v>
@@ -28511,7 +28511,7 @@
         <v>0.35</v>
       </c>
       <c r="H223">
-        <v>0.2409</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I223">
         <v>1300</v>
@@ -28535,7 +28535,7 @@
         <v>14</v>
       </c>
       <c r="R223" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S223" t="s">
         <v>351</v>
@@ -28570,7 +28570,7 @@
         <v>0.35</v>
       </c>
       <c r="H224">
-        <v>0.2482</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I224">
         <v>1300</v>
@@ -28629,7 +28629,7 @@
         <v>0.35</v>
       </c>
       <c r="H225">
-        <v>0.2482</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I225">
         <v>1300</v>
@@ -28688,7 +28688,7 @@
         <v>0.35</v>
       </c>
       <c r="H226">
-        <v>0.2482</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I226">
         <v>1300</v>
@@ -28747,7 +28747,7 @@
         <v>0.35</v>
       </c>
       <c r="H227">
-        <v>0.2482</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I227">
         <v>1300</v>
@@ -28806,7 +28806,7 @@
         <v>0.35</v>
       </c>
       <c r="H228">
-        <v>0.2482</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I228">
         <v>1300</v>
@@ -28865,7 +28865,7 @@
         <v>0.35</v>
       </c>
       <c r="H229">
-        <v>0.2482</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I229">
         <v>1300</v>
@@ -29137,7 +29137,7 @@
         <v>14</v>
       </c>
       <c r="R233" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S233" t="s">
         <v>351</v>
@@ -29199,7 +29199,7 @@
         <v>14</v>
       </c>
       <c r="R234" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S234" t="s">
         <v>351</v>
@@ -31679,7 +31679,7 @@
         <v>14</v>
       </c>
       <c r="R274" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S274" t="s">
         <v>351</v>
@@ -31741,7 +31741,7 @@
         <v>14</v>
       </c>
       <c r="R275" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S275" t="s">
         <v>351</v>
@@ -32113,7 +32113,7 @@
         <v>14</v>
       </c>
       <c r="R281" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S281" t="s">
         <v>351</v>
@@ -32175,7 +32175,7 @@
         <v>14</v>
       </c>
       <c r="R282" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S282" t="s">
         <v>351</v>
@@ -32361,7 +32361,7 @@
         <v>14</v>
       </c>
       <c r="R285" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S285" t="s">
         <v>351</v>
@@ -32423,7 +32423,7 @@
         <v>14</v>
       </c>
       <c r="R286" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S286" t="s">
         <v>351</v>
@@ -37164,7 +37164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD1EAA9D-A72A-4CC5-8B8B-CDD5C7FD0236}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E9C133-1EF0-4E76-A56A-ED4ADA3D24F5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_MEX/vt_vervestacks_MEX_v1.xlsx
+++ b/VerveStacks_MEX/vt_vervestacks_MEX_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0872750-8133-45EC-AFF2-C088886756AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D81E6A97-E2F2-4213-B709-E34A3D95E6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DCED2FD5-16A2-4A0D-A815-5A5FAA03A4B4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D4DF22AB-D0C6-4A24-9F1F-1F329AA3A940}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3277,7 +3277,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830A269C-81B5-464F-9B16-F90756ECF388}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654DE6CE-E3F4-439B-8E67-D0408BE58AFC}">
   <dimension ref="B9:V142"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9784,7 +9784,7 @@
         <v>14</v>
       </c>
       <c r="R114" t="s">
-        <v>926</v>
+        <v>830</v>
       </c>
       <c r="S114" t="s">
         <v>351</v>
@@ -9846,7 +9846,7 @@
         <v>14</v>
       </c>
       <c r="R115" t="s">
-        <v>830</v>
+        <v>926</v>
       </c>
       <c r="S115" t="s">
         <v>351</v>
@@ -11469,7 +11469,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47DE23D8-70B0-4CDB-A9DA-5488C73ABF14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E9F995-37E4-4018-AC0D-3CB965DB4784}">
   <dimension ref="B9:V81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15924,7 +15924,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AAA8B7-3DDF-4D6E-98AE-DEFD884252C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{996C42EF-2877-4767-B066-BE12C5708F27}">
   <dimension ref="B9:V402"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27529,7 +27529,7 @@
         <v>14</v>
       </c>
       <c r="R206" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S206" t="s">
         <v>351</v>
@@ -27588,7 +27588,7 @@
         <v>14</v>
       </c>
       <c r="R207" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S207" t="s">
         <v>351</v>
@@ -27647,7 +27647,7 @@
         <v>14</v>
       </c>
       <c r="R208" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S208" t="s">
         <v>351</v>
@@ -27706,7 +27706,7 @@
         <v>14</v>
       </c>
       <c r="R209" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S209" t="s">
         <v>351</v>
@@ -28951,7 +28951,7 @@
         <v>14</v>
       </c>
       <c r="R230" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S230" t="s">
         <v>351</v>
@@ -29013,7 +29013,7 @@
         <v>14</v>
       </c>
       <c r="R231" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S231" t="s">
         <v>351</v>
@@ -32113,7 +32113,7 @@
         <v>14</v>
       </c>
       <c r="R281" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S281" t="s">
         <v>351</v>
@@ -32175,7 +32175,7 @@
         <v>14</v>
       </c>
       <c r="R282" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S282" t="s">
         <v>351</v>
@@ -32237,7 +32237,7 @@
         <v>14</v>
       </c>
       <c r="R283" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="S283" t="s">
         <v>351</v>
@@ -32299,7 +32299,7 @@
         <v>14</v>
       </c>
       <c r="R284" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="S284" t="s">
         <v>351</v>
@@ -37164,7 +37164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E9C133-1EF0-4E76-A56A-ED4ADA3D24F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76BB637F-3588-42E6-B0F3-E7F71E656674}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
